--- a/data/derived_data/2_RarefyData/Conta_clusters_ITS.xlsx
+++ b/data/derived_data/2_RarefyData/Conta_clusters_ITS.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -38,10 +38,7 @@
     <t xml:space="preserve">Species</t>
   </si>
   <si>
-    <t xml:space="preserve">seed_sequence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_33</t>
+    <t xml:space="preserve">Cluster_26</t>
   </si>
   <si>
     <t xml:space="preserve">Fungi</t>
@@ -65,238 +62,124 @@
     <t xml:space="preserve">Unknown</t>
   </si>
   <si>
-    <t xml:space="preserve">TTAGTGAATGCCTGGGCTGTCATACGGACTGCGGTCTCTGACGCCCACCCACTATATCCGCAAACCCTGTGCACTGTGGTGTTGTCTTGGACACACCTCGCCAACCAACTCGTCTTTGTATCTGTACGTGTCTACTTGGCCTAAGCCAAAAATCAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_56</t>
+    <t xml:space="preserve">Cluster_42</t>
   </si>
   <si>
     <t xml:space="preserve">Malassezia restricta</t>
   </si>
   <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCAAAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCTTGGAGAAAGGCTTCAGAGAAGTTTTTTGTGGCCTCTCTTGGGGTCTTTCTTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCACAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCCTTGGAAAGGGCATTTGGAGAGAAAAAGGAAGAGAGAAGCGAGAACAGTGCGATCCGTCGCGTTGGGCGTTGATCTCTGGCTTGGTCTCTCTGAGGCCCTTTCCTCGCTACAAACTCGGATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_146</t>
+    <t xml:space="preserve">Cluster_60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_142</t>
   </si>
   <si>
     <t xml:space="preserve">Malassezia globosa</t>
   </si>
   <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGTATCCACTATACATCCATAAACCCGTGTGCACTGTTAAGGAGTAAGAAAGAAGGGGAGGGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCTCTTTCTCTTCCTTTCTCTCTCTGGTTAATTACACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_212</t>
+    <t xml:space="preserve">Cluster_225</t>
   </si>
   <si>
     <t xml:space="preserve">Malassezia sympodialis</t>
   </si>
   <si>
-    <t xml:space="preserve">TTAGTGAAAGTTTCGGGCCTGCCATACGGACGCAAACACGTCTCTGGCGCCCATCACTATATCCATACCAACCCCTGTGCACTGTGATGACGAATGTCATCGAACAAAAAAAACTCGTATGGTTGAATGTACGTGAAATTGTAGGTATAGCCTACGAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACGATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGGGGAGGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCTCACTCTCCACTCTCTTTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGAAGGGGGAGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCACTCTCTTTCTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGTATCCACTATACATCCATAAACCCGTGTGCACTGTTAAGGAGTAAGAAAGAAGAAGGGGAAGGGAGAGTGCATGTGCTTTGCATATAACTCTCTCTCTCTCTTCCTTTCTCTCTCTGGTTAATTACACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGAAGGGGGAGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCACTCTCTTTCTCTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATAAGGACGCCAAAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGGTCTTGGAGAAAGGCTTCAGAGAGGTTTTTTGTGGCCTCTCTTGGAGTCTTTTTCTTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGGGGAGGGGAGAGAGAGTGCATGTGCTTTGTATATAACTCTCTCTCACTCTCCACTCTCTTTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCAAAAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCTTGGAGAAAGGCTTCTTGAGAAGTTATGTGACCTCTCTTGGGGTCTTTCTTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_420</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCACAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCCTTGGAAAGGGCATTTGGAGAGAAAAAGGAAGAGAAGCGAGAACAGTGCGATCCGTCGCGTTGGGCGTTGATCTCTGGCTTGGTCTCTCTGAGGCCCTTTCCTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCAAAAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCTTGGAGAAAGGCTTCTTGAGAAGTTTTGTGGCCTCTCTTGGGGTCTTTCTTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCTTTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCAAAGAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGGTCTTGGAGAAAGGCTTCAGAGAAGTTTTTTGTGGCCTCTCTTGGAGTCTTTCTTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAATTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACGATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGGGGAGGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCTCACTCTCCACTCTCTTTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_1008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGTATCCACTATACATCCATAAACCCGTGTGCACTGTTAAGGAGTAAGAAAGAAGAAGGGGAAGGGAGAGTGCATGTGCTTTGCATATAACTCTCTCTCTCTTCCTTTCTCTCTCTGGTTAATTACACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_1246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTCTTGGAGAAAGGCTTCAGAGAAGTTTTTTGTGGCCTCTCTTGGGGTCTTTCTTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_1393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCAAAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCTTGGAGAAAGGCTTCAGAGAAGTTTTTTGTGGCCTCTCTGAGGCCCTTTCCTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_1504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCACAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCCTTGGAAAGGGCATTTGGAGAGAAAAAGAAAGAGAAGCGAGAGCAGTGCGATCCGTCGCGTTGGGCGTTTTCTCTGACTTGGTCTCTCTGAGGCCCTTTCCTTGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
+    <t xml:space="preserve">Cluster_252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_290</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_960</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_1002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_1020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_1251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_1503</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_1546</t>
   </si>
   <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGAAGGGGGAGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCACTCTCTTTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_1737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGAAGGGGGAGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCACACTCTTTCTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_1842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCACAAAGTGTCCCTGGCCGCCTACGCCCACTATACATCCACAAACCCGTGTGCACCGTCCTTGGAAAGGGCATTTGGAGAGAAAAAGGAAGAGAGAAGCGAGAACAGTGCGATCCGTCGCGTTGGGCGTTGATCTCTGGCTTGGTCTCTCTGAGGCCCTTTCCTCGCTACAAACTCGGATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_2064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCAAAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGAAGGGGGAGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCACTCTCTTTCTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_2112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGGGAGGGAGAGTAGCATGTGCTTTGCATATAACTCTCTCTCGCTCTCTTTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_2370</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGGGGGAGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCGCTCTCTTTCTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_2932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGTTTTGGGCAGGCCATACGGACGCCACAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCCTTGGAAAGGGCATTTTGAGAGAAAAAGGAAGAGAGAAGCGAGAACAGTGCGATCCGTCGCGTTGGGCGTTGATCTCTGGCTTGGTCTCTCTGAGGCCCTTTCCTCGCTACAAACTCGAATGGTTAGTATGAACGTGGAACTTGGTTGGACCGTCACTGACCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCACAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTGATGACGAATGTCATCGAACAAAAAAAAACTCGTATGGTTGAATGTACGTGAAATTGTAGGTATAGCCTACGAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGAAGGGGGAGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCACACTCTTTCTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATACGGACGCCAAAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGGGGAGGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCTCACTCTCCACTCTCTTTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCCTGCCATACGGACGCAAACACGTCTCTGGCGCCCATCACTATATCCATACCAACCCCTGTGCACTGTGATGACGAATGTCATCGAACAAAAAAAAACTCGTATGGTTGAATGTACGTGAAATTGTAGGTATAGCCTACGAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGTATCCACTATACATCCATAAACCCGTGTGCACTGTTAAGGAGTAAGAAAGAAGGGGAGGGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCTTTCTCTTCCTTTCTCTCTCTGGTTAATTACACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CTAGTGAAGATTTGGGCAGGCCATACGGACGCCACAAAGTGTCCCTGGCCGCCTACACCCACTATACATCCACAAACCCGTGTGCACTGTCCTTGGAAAGGGCATTTGGAGAGAAAAAGGAAGAGAGAAGCGAGAACAGTGCGATCCGTCGCGTTGGACGTTGATCTCTGGCTCGGTCTCTCTGAGGCCCTTTCCTCGCTACAAACTCGGATGGTTAGTATGAACGTAGAACTTGGTTGGACCGTCACTGGCCAACAAACTATACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCAGGCCATGCAGACGTACGATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGGGGAGGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCTCACTCTCCACTCTCTTTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_4057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACGATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGGGGGAGGGAGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCACACTCTTTCTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_4149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTCAAGGGCCAGCCATACAGACGTACAATAAGTGTGTCTCTGGCGGCTCGCATCCACTATACATCCATAAACCCGTGTGCACTGTTCTAAGGAGTAAGAAAGAAGAAGAAGGGGGAGGGAGAGAGTGCATGTGCTTTGCATATAACTCTCTCACTCTCCACACTCTTTCTCTCTCTCTCCGGTTAATTACAAACTCGTATGGATTTGTATGAACGTGAGATATATCGTTGGACCGTCACTGGCCAACAAATATAACAC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_15545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TTAGTGAAGATTTGGGCTGTCATACGGACTGCGGTCTCTGACGCCCACCCACTATATCCGCAAACCCTGTGCACTGTGGTGTTGTCTTGGACACACCTCACCAACCAACTCGTCTTTGTATCTGTACGTGTCTACTTGGCCTAAGCCAAAAATCAACAC</t>
+    <t xml:space="preserve">Cluster_1739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2070</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_2476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_3100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_3166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_3205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_3378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_3466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_3822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_4031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_4128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_4156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_4246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_7685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cluster_18132</t>
   </si>
 </sst>
 </file>
@@ -650,1110 +533,993 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H3" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H4" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H6" t="s">
-        <v>27</v>
-      </c>
-      <c r="I6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H7" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I9" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H12" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" t="s">
-        <v>19</v>
-      </c>
-      <c r="I13" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C14" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H14" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" t="s">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C15" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H15" t="s">
-        <v>19</v>
-      </c>
-      <c r="I15" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D16" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" t="s">
-        <v>48</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F17" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H17" t="s">
-        <v>19</v>
-      </c>
-      <c r="I17" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H18" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D19" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" t="s">
-        <v>54</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>19</v>
-      </c>
-      <c r="I20" t="s">
-        <v>56</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D21" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>19</v>
-      </c>
-      <c r="I21" t="s">
-        <v>58</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>59</v>
+        <v>38</v>
       </c>
       <c r="B22" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>19</v>
-      </c>
-      <c r="I22" t="s">
-        <v>60</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="B23" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C23" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="B24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C24" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" t="s">
-        <v>64</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>65</v>
+        <v>41</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D25" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" t="s">
-        <v>66</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>67</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" t="s">
-        <v>68</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>69</v>
+        <v>43</v>
       </c>
       <c r="B27" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C27" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D27" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" t="s">
-        <v>70</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
       <c r="B28" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="B29" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D29" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G29" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H29" t="s">
-        <v>19</v>
-      </c>
-      <c r="I29" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>75</v>
+        <v>46</v>
       </c>
       <c r="B30" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F30" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G30" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>27</v>
-      </c>
-      <c r="I30" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="B31" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D31" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F31" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G31" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="B32" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C32" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D32" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G32" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H32" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" t="s">
-        <v>80</v>
+        <v>15</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="B33" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C33" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D33" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G33" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H33" t="s">
-        <v>27</v>
-      </c>
-      <c r="I33" t="s">
-        <v>82</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C34" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D34" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H34" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" t="s">
-        <v>84</v>
+        <v>15</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D35" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G35" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H35" t="s">
-        <v>19</v>
-      </c>
-      <c r="I35" t="s">
-        <v>86</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C36" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E36" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H36" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" t="s">
-        <v>88</v>
+        <v>15</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>89</v>
+        <v>53</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C37" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D37" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" t="s">
-        <v>90</v>
+        <v>15</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>54</v>
       </c>
       <c r="B38" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D38" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E38" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" t="s">
-        <v>92</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>93</v>
+        <v>55</v>
       </c>
       <c r="B39" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C39" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D39" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E39" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G39" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" t="s">
-        <v>94</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/derived_data/2_RarefyData/Conta_clusters_ITS.xlsx
+++ b/data/derived_data/2_RarefyData/Conta_clusters_ITS.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="48">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -119,15 +119,9 @@
     <t xml:space="preserve">Cluster_960</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_1002</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_1020</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_1251</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_1503</t>
   </si>
   <si>
@@ -137,37 +131,19 @@
     <t xml:space="preserve">Cluster_1739</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_2070</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_2117</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_2476</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_3100</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_3205</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_3378</t>
   </si>
   <si>
-    <t xml:space="preserve">Cluster_3466</t>
-  </si>
-  <si>
     <t xml:space="preserve">Cluster_3822</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_4031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cluster_4128</t>
   </si>
   <si>
     <t xml:space="preserve">Cluster_4156</t>
@@ -999,7 +975,7 @@
         <v>14</v>
       </c>
       <c r="H19" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
@@ -1025,7 +1001,7 @@
         <v>14</v>
       </c>
       <c r="H20" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
@@ -1051,7 +1027,7 @@
         <v>14</v>
       </c>
       <c r="H21" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1077,7 +1053,7 @@
         <v>14</v>
       </c>
       <c r="H22" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
@@ -1155,7 +1131,7 @@
         <v>14</v>
       </c>
       <c r="H25" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26">
@@ -1181,7 +1157,7 @@
         <v>14</v>
       </c>
       <c r="H26" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="27">
@@ -1233,7 +1209,7 @@
         <v>14</v>
       </c>
       <c r="H28" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
@@ -1285,7 +1261,7 @@
         <v>14</v>
       </c>
       <c r="H30" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
@@ -1311,214 +1287,6 @@
         <v>14</v>
       </c>
       <c r="H31" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>48</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>13</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>49</v>
-      </c>
-      <c r="B33" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" t="s">
-        <v>13</v>
-      </c>
-      <c r="G33" t="s">
-        <v>14</v>
-      </c>
-      <c r="H33" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>50</v>
-      </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>13</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>51</v>
-      </c>
-      <c r="B35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" t="s">
-        <v>12</v>
-      </c>
-      <c r="F35" t="s">
-        <v>13</v>
-      </c>
-      <c r="G35" t="s">
-        <v>14</v>
-      </c>
-      <c r="H35" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>52</v>
-      </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
-        <v>13</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" t="s">
-        <v>12</v>
-      </c>
-      <c r="F37" t="s">
-        <v>13</v>
-      </c>
-      <c r="G37" t="s">
-        <v>14</v>
-      </c>
-      <c r="H37" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>54</v>
-      </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
-        <v>13</v>
-      </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>55</v>
-      </c>
-      <c r="B39" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" t="s">
-        <v>12</v>
-      </c>
-      <c r="F39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39" t="s">
-        <v>14</v>
-      </c>
-      <c r="H39" t="s">
         <v>15</v>
       </c>
     </row>
